--- a/安全体检报告/风险清单/安全事件表.xlsx
+++ b/安全体检报告/风险清单/安全事件表.xlsx
@@ -1023,6 +1023,7 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="38.6666666666667" customWidth="1" min="1" max="1"/>
+    <col width="18.1111111111111" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="17.3333333333333" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="19" max="19"/>
@@ -1347,7 +1348,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192.168.76.20</t>
+          <t>192.168.213.156</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1755,7 +1756,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>192.168.100.200</t>
+          <t>192.168.213.156</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1857,7 +1858,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>172.17.75.124</t>
+          <t>192.168.213.156</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1959,7 +1960,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>168.196.23.21</t>
+          <t>192.168.213.156</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2061,7 +2062,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>192.168.24.241</t>
+          <t>192.168.213.156</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2265,7 +2266,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>192.168.118.232</t>
+          <t>192.168.213.156</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">

--- a/安全体检报告/风险清单/安全事件表.xlsx
+++ b/安全体检报告/风险清单/安全事件表.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="事件表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'事件表'!$A$1:$W$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'事件表'!$A$1:$W$25</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,17 +26,17 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <name val="等线"/>
       <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="等线"/>
@@ -486,19 +486,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
@@ -507,7 +507,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
@@ -631,8 +631,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1015,18 +1017,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T25"/>
+  <dimension ref="A1:T64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="38.6666666666667" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="18.1111111111111" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14.4444444444444" customWidth="1" min="5" max="5"/>
+    <col width="20.1111111111111" customWidth="1" min="6" max="6"/>
     <col width="17.3333333333333" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="11.6666666666667" customWidth="1" min="17" max="17"/>
+    <col width="24.3333333333333" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1184,7 +1188,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>失陷</t>
+          <t>成功</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1348,7 +1352,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192.168.213.156</t>
+          <t>192.168.76.20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1542,7 +1546,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>incident-ccb79f5b-0c52-45c8-8727-a49ee56da964</t>
+          <t>incident-b1e6ff99-b2fc-44d0-894c-5c954ffa927e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1674,7 +1678,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>低危</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1756,7 +1760,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>192.168.213.156</t>
+          <t>192.168.100.200</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1776,7 +1780,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1858,7 +1862,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>192.168.213.156</t>
+          <t>172.17.75.124</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1878,1707 +1882,1303 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>处置完成</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>异常行为事件</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>DNS隧道</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>未成功</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-06-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>测试001</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>94.102.61.23</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>STA (B003EF),EDR (343300000000000008)</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>已推送</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>incident-08cddcf6-87ec-4051-91a1-1af581e6e57e</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>检测到海莲花APT攻击攻击活动—远程代码执行</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>168.196.23.21</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>主机失陷活动</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>勒索攻击</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>处理中</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>漏洞利用</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>远程代码执行</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>失陷</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>测试001</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>185.153.196.30</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>STA (B003F0),EDR (343300000000000009)</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2026-06-05 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>incident-c608fb20-d8e3-474b-b827-6b17c3cfc628</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>检测到响尾蛇APT攻击攻击活动—蠕虫传播</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>192.168.24.241</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>主机失陷活动</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>勒索攻击</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>低危</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>处置完成</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>异常行为事件</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>恶意程序事件</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>蠕虫传播</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-06-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-06-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>测试001</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>146.185.239.120</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>STA (B003F1),EDR (343300000000000010)</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>已推送</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>2026-05-31 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>incident-db2b4387-6cc5-49c0-90ce-5babab227c1b</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>检测到cobaltstrike远控攻击活动—CobaltStrike</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10.245.224.255</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>主机失陷活动</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>cobaltstrike远控</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>渗透攻击事件</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CobaltStrike</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-06-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>测试001</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>195.123.237.91</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>STA (B003F2),EDR (343300000000000011)</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>处置中</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2026-06-05 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>incident-4d1c559a-2cdb-4ad9-95de-752d013f9501</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>检测到摩诃草APT攻击活动—DNS隧道</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>192.168.118.232</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>主机失陷活动</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>摩诃草APT</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>处理中</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>恶意程序事件</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>DNS隧道</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>未成功</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2026-06-03 00:00:00</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>2026-06-05 00:00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>测试001</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>94.102.61.23</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>STA (B003EF),EDR (343300000000000008)</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>45.155.205.99</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>STA (B003F3),EDR (343300000000000012)</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>已处置</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>incident-63d36b46-77cd-400f-be38-b920e711ce7d</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>检测到银狐病毒活动—病毒木马行为</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>192.168.254.90</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>病毒木马活动</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>银狐病毒</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>恶意程序事件</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>病毒木马行为</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>测试001</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>198.54.117.210</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>EDR (343300000000000100),STA (A07D0)</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>处置中</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2026-06-18 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>incident-c7df0a06-bb71-46ee-8628-e29f645a93d7</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>检测到勒索病毒活动—WebShell上传</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10.16.11.65</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>病毒木马活动</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>勒索病毒</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>处置完成</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>恶意程序事件</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>WebShell上传</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>未成功</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-06-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>测试001</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>EDR (343300000000000101),STA (A07D1)</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>已推送</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2026-06-02 22:00:00</t>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>2026-06-05 23:00:00</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="8" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>incident-08cddcf6-87ec-4051-91a1-1af581e6e57e</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>检测到海莲花APT攻击攻击活动—远程代码执行</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>192.168.213.156</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>主机失陷活动</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>勒索攻击</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>incident-6070271d-a3e1-4801-8c67-6f895ecbf435</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>检测到挖矿病毒活动—数据窃取</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10.18.20.115</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>病毒木马活动</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>挖矿病毒</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>处置完成</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>恶意程序事件</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>数据窃取</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>失陷</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-06-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>测试001</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>EDR (343300000000000102),STA (A07D2)</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>已推送</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2026-06-18 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>incident-394abd11-137d-431b-8a49-52c69b4dce5b</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>检测到后门木马活动—文件上传漏洞</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>172.20.64.95</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>病毒木马活动</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>后门木马</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>漏洞利用</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>文件上传漏洞</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>测试001</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5.188.206.78</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>EDR (343300000000000103),STA (A07D3)</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>已遏制</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-06-26 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>incident-58f520ea-72d3-4486-8e3f-040755ed7750</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>检测到下载者木马活动—蠕虫传播</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>192.168.50.10</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>病毒木马活动</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>下载者木马</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>处理中</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>恶意程序事件</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>蠕虫传播</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-06-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>测试001</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>EDR (343300000000000104),STA (A07D4)</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>处置中</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-06-02 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>incident-9acde1de-c665-49d3-8a14-a2fe7dd5af2a</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>检测到蠕虫病毒活动—CobaltStrike</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10.100.1.50</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>病毒木马活动</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>蠕虫病毒</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>已忽略</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>渗透攻击事件</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CobaltStrike</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>未成功</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-06-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-06-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>测试001</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>EDR (343300000000000105),STA (A07D5)</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>已处置</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-06-16 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>incident-4710a104-1d6c-43de-a936-4fe1675306d0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>检测到银狐病毒活动—数据窃取</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>172.16.88.30</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>病毒木马活动</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>银狐病毒</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>渗透攻击事件</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>数据窃取</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>失陷</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-06-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-06-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>测试001</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>146.185.239.120</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>EDR (343300000000000106),STA (A07D6)</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-06-05 23:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>incident-fcab63d5-eb97-44bf-bf5d-af93ceb520af</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>检测到勒索病毒活动—系统漏洞攻击</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>192.168.1.100</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>病毒木马活动</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>勒索病毒</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>处理中</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>处置完成</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>漏洞利用</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>远程代码执行</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>失陷</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-06-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>系统漏洞攻击</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>攻击</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-06-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-06-05 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>测试001</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>185.153.196.30</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>STA (B003F0),EDR (343300000000000009)</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2026-06-05 22:00:00</t>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>EDR (343300000000000107),STA (A07D7)</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>已遏制</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-06-03 23:00:00</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="8" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>incident-c608fb20-d8e3-474b-b827-6b17c3cfc628</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>检测到响尾蛇APT攻击攻击活动—蠕虫传播</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>192.168.213.156</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>主机失陷活动</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>勒索攻击</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>处置完成</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>恶意程序事件</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>蠕虫传播</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2026-06-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-06-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>146.185.239.120</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>STA (B003F1),EDR (343300000000000010)</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>已推送</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2026-05-31 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="8" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>incident-db2b4387-6cc5-49c0-90ce-5babab227c1b</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>检测到cobaltstrike远控攻击活动—CobaltStrike</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>10.245.224.255</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>主机失陷活动</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>cobaltstrike远控</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>渗透攻击事件</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>CobaltStrike</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-06-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>195.123.237.91</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>STA (B003F2),EDR (343300000000000011)</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>处置中</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2026-06-05 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="8" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>incident-4d1c559a-2cdb-4ad9-95de-752d013f9501</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>检测到摩诃草APT攻击活动—DNS隧道</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>192.168.213.156</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>主机失陷活动</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>摩诃草APT</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>处理中</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>恶意程序事件</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>DNS隧道</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>未成功</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2026-06-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2026-06-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>45.155.205.99</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>STA (B003F3),EDR (343300000000000012)</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>已处置</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-06-02 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="8" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>incident-63d36b46-77cd-400f-be38-b920e711ce7d</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>检测到银狐病毒活动—病毒木马行为</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>192.168.100.200</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>银狐病毒</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>恶意程序事件</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>病毒木马行为</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>2026-06-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>198.54.117.210</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000100),STA (A07D0)</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>处置中</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-06-18 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="8" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>incident-c7df0a06-bb71-46ee-8628-e29f645a93d7</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>检测到勒索病毒活动—WebShell上传</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>172.17.75.124</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>勒索病毒</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>处置完成</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>恶意程序事件</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>WebShell上传</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>未成功</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-06-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000101),STA (A07D1)</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>已推送</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>2026-06-05 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="8" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>incident-6070271d-a3e1-4801-8c67-6f895ecbf435</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>检测到挖矿病毒活动—数据窃取</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>168.196.23.21</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>挖矿病毒</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>处置完成</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>恶意程序事件</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>数据窃取</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>失陷</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2026-06-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-06-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000102),STA (A07D2)</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>已推送</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-06-18 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="8" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>incident-394abd11-137d-431b-8a49-52c69b4dce5b</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>检测到后门木马活动—文件上传漏洞</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>192.168.24.241</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>后门木马</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>漏洞利用</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>文件上传漏洞</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>2026-06-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2026-06-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>5.188.206.78</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000103),STA (A07D3)</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>已遏制</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>2026-06-26 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="8" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>incident-58f520ea-72d3-4486-8e3f-040755ed7750</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>检测到下载者木马活动—蠕虫传播</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>10.245.224.255</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>下载者木马</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>处理中</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>恶意程序事件</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>蠕虫传播</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>2026-06-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2026-06-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000104),STA (A07D4)</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>处置中</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-06-02 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="8" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>incident-9acde1de-c665-49d3-8a14-a2fe7dd5af2a</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>检测到蠕虫病毒活动—CobaltStrike</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>192.168.118.232</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>蠕虫病毒</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>已忽略</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>渗透攻击事件</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>CobaltStrike</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>未成功</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>2026-06-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2026-06-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000105),STA (A07D5)</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>已处置</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026-06-16 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="8" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>incident-4710a104-1d6c-43de-a936-4fe1675306d0</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>检测到银狐病毒活动—数据窃取</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>192.168.254.90</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>银狐病毒</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>渗透攻击事件</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>数据窃取</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>失陷</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2026-06-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-06-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>146.185.239.120</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000106),STA (A07D6)</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2026-06-05 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="8" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>incident-fcab63d5-eb97-44bf-bf5d-af93ceb520af</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>检测到勒索病毒活动—系统漏洞攻击</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>10.16.11.65</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>勒索病毒</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>处置完成</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>漏洞利用</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>系统漏洞攻击</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2026-06-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-06-05 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000107),STA (A07D7)</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>已遏制</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2026-06-03 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="8" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>incident-c7957788-18d6-4da3-a6bd-68df798fa694</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>检测到挖矿病毒活动—后门程序</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>10.18.20.115</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>挖矿病毒</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>已忽略</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>渗透攻击事件</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>后门程序</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-06-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2026-06-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000108),STA (A07D8)</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>处置中</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>2026-06-23 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="8" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>incident-1c4381dc-4e32-4103-8cef-e815f739fdc3</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>检测到后门木马活动—横向移动</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>172.20.64.95</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>后门木马</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>已处理</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>渗透攻击事件</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>横向移动</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>未成功</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2026-06-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-06-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>45.33.32.156</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000109),STA (A07D9)</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>已处置</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>2026-06-28 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="8" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>incident-4d305f2c-7272-43c2-8fbe-494cb9e5061d</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>检测到下载者木马活动—数据窃取</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>192.168.50.10</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>下载者木马</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>处理中</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>异常行为事件</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>数据窃取</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>失陷</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2026-06-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2026-06-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000110),STA (A07DA)</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>2026-06-10 23:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="8" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>incident-dc299149-042b-4c79-93f3-5fb385480412</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>检测到蠕虫病毒活动—命令注入</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>10.100.1.50</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>病毒木马活动</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>蠕虫病毒</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>已忽略</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>渗透攻击事件</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>命令注入</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2026-06-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2026-06-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>测试001</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>EDR (343300000000000111),STA (A07DB)</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>已遏制</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-06-25 23:00:00</t>
-        </is>
-      </c>
-    </row>
+    <row r="22" hidden="1"/>
+    <row r="23" hidden="1"/>
+    <row r="24" hidden="1"/>
+    <row r="25" hidden="1"/>
     <row r="26" ht="8" customHeight="1"/>
     <row r="27" ht="8" customHeight="1"/>
     <row r="28" ht="8" customHeight="1"/>
@@ -3678,33 +3278,15 @@
     <row r="122" ht="8" customHeight="1"/>
     <row r="123" ht="8" customHeight="1"/>
     <row r="124" ht="8" customHeight="1"/>
-    <row r="125" ht="8" customHeight="1"/>
-    <row r="126" ht="8" customHeight="1"/>
-    <row r="127" ht="8" customHeight="1"/>
-    <row r="128" ht="8" customHeight="1"/>
-    <row r="129" ht="8" customHeight="1"/>
-    <row r="130" ht="8" customHeight="1"/>
-    <row r="131" ht="8" customHeight="1"/>
-    <row r="132" ht="8" customHeight="1"/>
-    <row r="133" ht="8" customHeight="1"/>
-    <row r="134" ht="8" customHeight="1"/>
-    <row r="135" ht="8" customHeight="1"/>
-    <row r="136" ht="8" customHeight="1"/>
-    <row r="137" ht="8" customHeight="1"/>
-    <row r="138" ht="8" customHeight="1"/>
-    <row r="139" ht="8" customHeight="1"/>
-    <row r="140" ht="8" customHeight="1"/>
-    <row r="141" ht="8" customHeight="1"/>
-    <row r="142" ht="8" customHeight="1"/>
-    <row r="143" ht="8" customHeight="1"/>
-    <row r="144" ht="8" customHeight="1"/>
-    <row r="145" ht="8" customHeight="1"/>
-    <row r="146" ht="8" customHeight="1"/>
-    <row r="147" ht="8" customHeight="1"/>
-    <row r="148" ht="8" customHeight="1"/>
-    <row r="149" ht="8" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:W57"/>
+  <autoFilter ref="A1:W25">
+    <filterColumn colId="4" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="主机失陷活动"/>
+        <filter val="病毒木马活动"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/安全体检报告/风险清单/安全事件表.xlsx
+++ b/安全体检报告/风险清单/安全事件表.xlsx
@@ -1173,7 +1173,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>已忽略</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>处理中</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>处理中</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>处理中</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>处理中</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>高危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>中危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>处理中</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>已忽略</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>已处理</t>
+          <t>处置完成</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">

--- a/安全体检报告/风险清单/安全事件表.xlsx
+++ b/安全体检报告/风险清单/安全事件表.xlsx
@@ -631,11 +631,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1017,14 +1016,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="42.1111111111111" customWidth="1" min="1" max="1"/>
+    <col width="20.7777777777778" customWidth="1" min="2" max="2"/>
     <col width="18.1111111111111" customWidth="1" min="3" max="3"/>
     <col width="14.4444444444444" customWidth="1" min="5" max="5"/>
     <col width="20.1111111111111" customWidth="1" min="6" max="6"/>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>漏洞利用</t>
+          <t>恶意程序事件</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>已推送</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>incident-89635cc4-1b23-44ca-a765-19ccf893c446</t>
+          <t>incident-ccb79f5b-0c52-45c8-8727-a49ee56da964</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>192.168.213.156</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>吃粽子</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>已遏制</t>
+          <t>已推送</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>192.168.76.20</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>192.168.200.33</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>192.168.200.22</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>漏洞利用</t>
+          <t>恶意程序事件</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>192.168.100.205</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>192.168.100.200</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>172.17.75.124</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>168.196.23.21</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>漏洞利用</t>
+          <t>恶意程序事件</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>192.168.24.241</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10.245.224.255</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>主机失陷活动</t>
+          <t>病毒木马活动</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>192.168.118.232</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>主机失陷活动</t>
+          <t>病毒木马活动</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>192.168.254.90</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10.16.11.65</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10.18.20.115</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>172.20.64.95</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>漏洞利用</t>
+          <t>恶意程序事件</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>192.168.50.10</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10.100.1.50</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>病毒木马活动</t>
+          <t>123活动</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>渗透攻击事件</t>
+          <t>漏洞利用事件</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>172.16.88.30</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>病毒木马活动</t>
+          <t>124活动</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>渗透攻击事件</t>
+          <t>漏洞利用事件</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>192.168.1.100</t>
+          <t>10.248.38.136</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>病毒木马活动</t>
+          <t>125活动</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>处置完成</t>
+          <t>处置中</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>漏洞利用</t>
+          <t>漏洞利用事件</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3175,26 +3175,26 @@
         </is>
       </c>
     </row>
-    <row r="22" hidden="1"/>
-    <row r="23" hidden="1"/>
-    <row r="24" hidden="1"/>
-    <row r="25" hidden="1"/>
-    <row r="26" ht="8" customHeight="1"/>
-    <row r="27" ht="8" customHeight="1"/>
-    <row r="28" ht="8" customHeight="1"/>
-    <row r="29" ht="8" customHeight="1"/>
-    <row r="30" ht="8" customHeight="1"/>
-    <row r="31" ht="8" customHeight="1"/>
-    <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="8" customHeight="1"/>
-    <row r="34" ht="8" customHeight="1"/>
-    <row r="35" ht="8" customHeight="1"/>
-    <row r="36" ht="8" customHeight="1"/>
-    <row r="37" ht="8" customHeight="1"/>
-    <row r="38" ht="8" customHeight="1"/>
-    <row r="39" ht="8" customHeight="1"/>
-    <row r="40" ht="8" customHeight="1"/>
-    <row r="41" ht="8" customHeight="1"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
     <row r="42" ht="8" customHeight="1"/>
     <row r="43" ht="8" customHeight="1"/>
     <row r="44" ht="8" customHeight="1"/>
@@ -3279,14 +3279,7 @@
     <row r="123" ht="8" customHeight="1"/>
     <row r="124" ht="8" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:W25">
-    <filterColumn colId="4" hiddenButton="0" showButton="1">
-      <filters>
-        <filter val="主机失陷活动"/>
-        <filter val="病毒木马活动"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:W25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/安全体检报告/风险清单/安全事件表.xlsx
+++ b/安全体检报告/风险清单/安全事件表.xlsx
@@ -14281,7 +14281,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>勒索攻击</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>勒索攻击</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -14863,7 +14863,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>银狐病毒</t>
+          <t>勒索攻击</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
